--- a/figures/excel/Table_S5.xlsx
+++ b/figures/excel/Table_S5.xlsx
@@ -2599,7 +2599,7 @@
     <row r="47" ht="34" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>NOTE: PMIDs and extracted HPO terms only. No article text is reproduced (Gate G7).</t>
+          <t>NOTE: PMIDs and extracted HPO terms only. No article text is reproduced.</t>
         </is>
       </c>
     </row>
